--- a/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>聲音由什麼產生？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>物體振動</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>振動發聲</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>聲音以哪種波傳播？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>聽不到</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>縱波</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>疏密波</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>聲音傳播需要什麼？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>介質</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>光速&gt;聲速</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>固液氣</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>真空能傳聲嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>無介質</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>室溫空氣中聲速約？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>分子排列緊密傳遞有效</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>約1020 m</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>340 m/s</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不同距離放電回聲交疊</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>常用值</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>聲速在固液氣何者最快？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>固體</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>真空不傳聲</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>分子密</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>聲波遇障礙反射形成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>真空不傳聲</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>回聲</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>聽不到</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>振動停止聲音會？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>無振動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>人說話發聲靠什麼振動？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>聲帶</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>振動</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>聲音在什麼中不能傳播？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>聽不到</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>變快</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>真空</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>無介質</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>聲速在氣體最慢的原因？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>分子排列緊密傳遞有效</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>分子間距大傳遞慢</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>約1020 m</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不同距離放電回聲交疊</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>介質特性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>溫度升高聲速如何變？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>聽不到</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>變快</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>真空不傳聲</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分子運動快</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>回聲2秒後聽到，障礙距離(340m/s)？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>340 m</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>750 m</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>680 m</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>425 m</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>340×2÷2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>聲納在水中利用什麼？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>回聲測距</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>太空人如何溝通？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>靠無線電</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>真空不傳聲</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>打雷先閃後聲因為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>光速&gt;聲速</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>傳播速度差</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>聲音在水中比空氣快嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>回聲</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>變快</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>液&gt;氣</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>鼓聲來自？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>變快</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>光速&gt;聲速</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>聽不到</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>鼓面振動</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>發聲體</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>聲速在鋼鐵中比空氣中？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>回聲測距</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>真空不傳聲</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>固體快</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>氣溫上升時空氣中聲速會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>變快</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上3-2 聲音的產生與傳播　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>看到閃電3秒後聽雷聲，距離約？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>分子間距大傳遞慢</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>分子排列緊密傳遞有效</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>約1020 m</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>340 m/s</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>340×3</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何固體傳聲最快？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>約1020 m</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>分子間距大傳遞慢</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>分子排列緊密傳遞有效</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不同距離放電回聲交疊</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>介質結構</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>回聲測井深，聲來回4秒(340)，井深？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>340 m</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>750 m</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>425 m</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>680 m</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>340×4÷2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>潛艇聲納測到回波1秒(水中1500m/s)，目標距離？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>680 m</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>750 m</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>340 m</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>425 m</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>1500×1÷2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>在月球敲鑼聽得到嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>光速&gt;聲速</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>固體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>聽不到</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>真空</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>聲音三態介質皆可傳，最有效是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>變快</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>固體</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>傳最快</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>雷聲隆隆不斷是因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>不同距離放電回聲交疊</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>約1020 m</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>分子間距大傳遞慢</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>340 m/s</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>多重反射</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>設計實驗測空氣聲速需量什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>距離與時間</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>v=d/t</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>對山谷喊叫2.5秒後聽到回聲(340)距離？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>750 m</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>340 m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>425 m</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>680 m</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>340×2.5÷2</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何太空爆炸無聲是正確的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>物體振動</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>鼓面振動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>真空不傳聲</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>真空</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>不同距離放電回聲交疊</t>
+          <t>閃電路徑長,各段聲音抵達時間不同</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>不同距離放電回聲交疊</t>
+          <t>閃電路徑長,各段聲音抵達時間不同</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>不同距離放電回聲交疊</t>
+          <t>閃電路徑長,各段聲音抵達時間不同</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>不同距離放電回聲交疊</t>
+          <t>閃電路徑長,各段聲音抵達時間不同</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>多重反射</t>
+          <t>路徑各點距離不同</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>振動發聲</t>
+          <t>振動發聲：任何聲音的來源都是物體振動，振動使周圍空氣產生疏密變化，形成聲波</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>疏密波</t>
+          <t>疏密波：聲音靠介質分子一疏一密振動來傳遞，振動方向和傳播方向平行，屬於縱波</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>固液氣</t>
+          <t>固液氣：聲音需要靠固體、液體或氣體等介質來傳遞，沒有介質就無法傳播</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>無介質</t>
+          <t>無介質：真空中沒有可以振動傳遞聲音的介質(分子)，所以聲音無法在真空中傳播</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>常用值</t>
+          <t>常用值：一般室溫下，聲音在空氣中傳播的速度大約是340公尺/秒，是常用的計算數值</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>分子密</t>
+          <t>分子密：固體分子排列最緊密，振動能快速傳給鄰近分子，所以聲音在固體中傳播得最快</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：聲波遇到障礙物反彈回來、再次被聽到的現象稱為回聲，是聲音的反射</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無振動</t>
+          <t>無振動：聲音的來源是物體振動，一旦振動停止，就不再產生新的聲波，聲音也會跟著停止</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>振動</t>
+          <t>振動：人說話時，氣流通過喉嚨使聲帶產生振動，這個振動就是聲音的來源</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>無介質</t>
+          <t>無介質：聲音需要靠介質(如空氣、水)的分子振動來傳遞，真空中沒有可以振動的介質，所以聲音無法傳播</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>介質特性</t>
+          <t>介質特性：氣體分子間距離較大，振動要傳到鄰近分子需要較長時間，所以聲音在氣體中傳播得比固體、液體慢</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分子運動快</t>
+          <t>分子運動快：溫度越高，分子運動越劇烈，聲音傳遞的速度也會隨之變快</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>340×2÷2</t>
+          <t>340×2÷2：聲音來回共花2秒，單程距離=波速×時間÷2，340乘以2再除以2等於340公尺</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：聲納發出聲波，遇到物體反射回來，靠測量來回時間換算出距離，原理是聲音的反射</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>真空不傳聲</t>
+          <t>真空不傳聲：太空是接近真空的環境，聲音無法傳播，太空人必須靠無線電波(不需要介質)來溝通</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傳播速度差</t>
+          <t>傳播速度差：光的速度遠遠快於聲音的速度，所以我們會先看到閃電，過一段時間才聽到雷聲</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>液&gt;氣</t>
+          <t>液&gt;氣：液體分子排列比氣體緊密，聲音在液體中傳遞的速度比在氣體中快</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發聲體</t>
+          <t>發聲體：敲擊鼓面使鼓皮上下振動，這個振動就是鼓聲的來源</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>固體快</t>
+          <t>固體快：一般來說固體分子排列緊密，振動傳遞效率高，所以聲音在鋼鐵等固體中傳播的速度比在空氣中快很多</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度：空氣溫度越高，分子運動越劇烈，聲音傳遞的速度也會隨之變快</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>340×3</t>
+          <t>340×3：光速極快幾乎瞬間看到，聲音走完全程需要3秒，距離=波速×時間=340×3=1020公尺</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>介質結構</t>
+          <t>介質結構：固體分子排列緊密、彼此距離近，振動能量能更有效率地一個接一個傳給鄰近分子，所以傳聲速度最快</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>340×4÷2</t>
+          <t>340×4÷2：聲音來回共花4秒，單程距離=波速×時間÷2，340乘以4再除以2等於680公尺</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1500×1÷2</t>
+          <t>1500×1÷2：聲音在水中來回共花1秒，單程距離=波速×時間÷2，1500乘以1再除以2等於750公尺</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>真空：月球表面幾乎沒有大氣、接近真空，沒有介質可以傳遞聲音，所以聽不到鑼聲</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>傳最快</t>
+          <t>傳最快：聲音可以在固、液、氣三態中傳播，但固體分子排列最緊密，傳遞效率最好、速度最快</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>路徑各點距離不同</t>
+          <t>路徑各點距離不同：閃電路徑很長，各段聲音發生點與聽者的距離不同，抵達耳朵的時間先後分散，所以聽起來雷聲連續不斷</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>v=d/t</t>
+          <t>v=d/t：波速=距離÷時間，只要測出聲音走過的距離和所花的時間，就能算出聲速</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>340×2.5÷2</t>
+          <t>340×2.5÷2：聲音來回共花2.5秒，單程距離=波速×時間÷2，340乘以2.5再除以2等於425公尺</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>真空：太空幾乎是真空環境，沒有空氣等介質可以傳遞聲波，所以就算發生爆炸，遠處的太空中也聽不到聲音，這符合聲音需要介質才能傳播的原理</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-2_三種難度測驗卷.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>物體振動</t>
+          <t>縱波</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>真空不傳聲</t>
+          <t>停止</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>靠無線電</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>停止</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>真空</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>變快</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>真空</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>固體</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>聽不到</t>
+          <t>固體</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>介質</t>
+          <t>回聲</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>真空不傳聲</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>固體</t>
+          <t>縱波</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>距離與時間</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1279,14 +1279,14 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>靠無線電</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>停止</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>回聲</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>快</t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>變快</t>
+          <t>物體振動</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>物體振動</t>
+          <t>靠無線電</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>回聲測距</t>
+          <t>回聲</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>真空不傳聲</t>
+          <t>停止</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>物體振動</t>
+          <t>真空</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>縱波</t>
+          <t>介質</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>固體</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>物體振動</t>
+          <t>固體</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>縱波</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
